--- a/英语群_20260829.xlsx
+++ b/英语群_20260829.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F431082F944467EC6983988F08D5072EBBFCCB0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F431082F942460F13123E61708C3372FBBFCCB0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16890" yWindow="50" windowWidth="19720" windowHeight="20950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -638,15 +638,15 @@
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -752,20 +752,20 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="E4" s="3">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
       <c r="F4" s="5">
         <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="25">
         <v>24</v>
@@ -962,20 +962,20 @@
       </c>
       <c r="D9" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="25">
         <v>24</v>
@@ -1000,21 +1000,21 @@
       </c>
       <c r="C10" s="3">
         <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="D10" s="3">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
       <c r="E10" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="F10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="2"/>
@@ -1218,16 +1218,16 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
       </c>
       <c r="H15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="25">
         <v>28</v>
@@ -1336,21 +1336,21 @@
       </c>
       <c r="C18" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F18" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="5">
         <v>0</v>
@@ -1634,20 +1634,20 @@
       </c>
       <c r="D25" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" s="5">
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="25">
         <v>22</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="2"/>
@@ -1722,16 +1722,16 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5">
         <v>0</v>
       </c>
       <c r="H27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="25">
         <v>9</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="2"/>
@@ -1932,16 +1932,16 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
         <v>0</v>
       </c>
       <c r="H32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="25">
         <v>28</v>
@@ -2054,20 +2054,20 @@
       </c>
       <c r="D35" s="3">
         <f t="shared" ref="D35:D52" si="6">G35+K35</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" s="3">
         <f t="shared" ref="E35:E52" si="7">H35+L35</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="25">
         <v>27</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C36" s="3">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="6"/>
@@ -2100,16 +2100,16 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="5">
         <v>0</v>
       </c>
       <c r="H36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="25">
         <v>28</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C38" s="3">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="3">
         <f t="shared" si="6"/>
@@ -2184,16 +2184,16 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F38" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="5">
         <v>0</v>
       </c>
       <c r="H38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="25">
         <v>21</v>
@@ -2222,20 +2222,20 @@
       </c>
       <c r="D39" s="3">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="25">
         <v>23</v>
@@ -2596,21 +2596,21 @@
       </c>
       <c r="C48" s="3">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="F48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="5">
         <v>0</v>

--- a/英语群_20260829.xlsx
+++ b/英语群_20260829.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F431082F942460F13123E61708C3372FBBFCCB0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F431082F9404E1B2F921064FC9F1872EBBFCCB0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16890" yWindow="50" windowWidth="19720" windowHeight="20950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,11 +642,11 @@
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="2"/>
@@ -756,16 +756,16 @@
       </c>
       <c r="E4" s="3">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="25">
         <v>24</v>
@@ -962,20 +962,20 @@
       </c>
       <c r="D9" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="25">
         <v>24</v>
@@ -1004,20 +1004,20 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="25">
         <v>22</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3">
         <f t="shared" si="2"/>
@@ -1260,16 +1260,16 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
       </c>
       <c r="H16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="25">
         <v>20</v>
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D18" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="25">
         <v>18</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C20" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="3">
         <f t="shared" si="2"/>
@@ -1428,16 +1428,16 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5">
         <v>0</v>
       </c>
       <c r="H20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="25">
         <v>28</v>
@@ -1634,20 +1634,20 @@
       </c>
       <c r="D25" s="3">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5">
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="25">
         <v>22</v>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="5">
         <v>0</v>
@@ -1798,21 +1798,21 @@
       </c>
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" s="3">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="5">
         <v>0</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" s="3">
         <f t="shared" si="2"/>
@@ -1848,16 +1848,16 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5">
         <v>0</v>
       </c>
       <c r="H30" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="25">
         <v>28</v>
@@ -2054,20 +2054,20 @@
       </c>
       <c r="D35" s="3">
         <f t="shared" ref="D35:D52" si="6">G35+K35</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" s="3">
         <f t="shared" ref="E35:E52" si="7">H35+L35</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="25">
         <v>27</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C36" s="3">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="6"/>
@@ -2100,16 +2100,16 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5">
         <v>0</v>
       </c>
       <c r="H36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="25">
         <v>28</v>
@@ -2218,21 +2218,21 @@
       </c>
       <c r="C39" s="3">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="3">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="F39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5">
         <v>0</v>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="D45" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" s="3">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" s="5">
         <v>0</v>
       </c>
       <c r="G45" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="25">
         <v>19</v>
@@ -2600,20 +2600,20 @@
       </c>
       <c r="D48" s="3">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" s="5">
         <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="25">
         <v>28</v>
@@ -2642,20 +2642,20 @@
       </c>
       <c r="D49" s="3">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="25">
         <v>26</v>
